--- a/08_RQ5_TeamPlus_Followup.xlsx
+++ b/08_RQ5_TeamPlus_Followup.xlsx
@@ -506,7 +506,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RQ5 Formative Follow-Up: TeamPlus Hands-On Case (VienaSmart)</t>
+          <t>RQ5 Formative Follow-Up: TeamPlus Hands-On Case (ProjetoVS)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -548,7 +548,7 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>After the asynchronous RQ5 comparison/acceptability workbook was returned and reviewed in a recorded member-check, the staffing authority configured a new project case (six-person team, an industrial furnace/energy-sensing recommendation and monitoring system, internally labeled "VienaSmart") directly in the TeamPlus tool.</t>
+          <t>After the asynchronous RQ5 comparison/acceptability workbook was returned and reviewed in a recorded member-check, the staffing authority configured a new project case (six-person team, an industrial furnace/energy-sensing recommendation and monitoring system) directly in the TeamPlus tool. The case is anonymized in this workbook as "ProjetoVS".</t>
         </is>
       </c>
     </row>
@@ -657,14 +657,14 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>No experimental value was corrected, rounded, reordered, filtered, or recomputed in the TeamPlus Ranked Teams or Accepted Team sheets. Developer identifiers (e.g., "Dev370") are preserved verbatim as source identifiers; the project label "VienaSmart" is the internal case name used by the tool and is preserved as-is.</t>
+          <t>No experimental value was corrected, rounded, reordered, filtered, or recomputed in the TeamPlus Ranked Teams or Accepted Team sheets. Developer identifiers (e.g., "Dev370") are preserved verbatim as source identifiers. The tool's internal case name for this project was "VienaSmart" in the source data; per explicit author request, that label was replaced throughout this workbook with the anonymized case name "ProjetoVS" (source file names on disk, listed in Source Manifest, are unaffected).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>This workbook was built from the VienaSmart source files located alongside the RQ5 expert-validation material, not from "Experimento_TeamPlus_Consistencia" (a separate, unrelated set of thirteen synthetic four-person test projects with no connection to this six-person case; it contains no VienaSmart data).</t>
+          <t>This workbook was built from the source files for this hands-on case (internally named "vienasmart" on disk) located alongside the RQ5 expert-validation material, not from "Experimento_TeamPlus_Consistencia" (a separate, unrelated set of thirteen synthetic four-person test projects with no connection to this six-person case).</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
     </row>
@@ -1061,77 +1061,77 @@
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>Domain MUST</t>
+          <t>AD MUST</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>Domain SHOULD</t>
+          <t>AD SHOULD</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>Domain COULD</t>
+          <t>AD COULD</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem MUST</t>
+          <t>DE MUST</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem SHOULD</t>
+          <t>DE SHOULD</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem COULD</t>
+          <t>DE COULD</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>Language MUST</t>
+          <t>PL MUST</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>Language SHOULD</t>
+          <t>PL SHOULD</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>Language COULD</t>
+          <t>PL COULD</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>Domain Score</t>
+          <t>AD Score</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>Domain Classification</t>
+          <t>AD Classification</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem Score</t>
+          <t>DE Score</t>
         </is>
       </c>
       <c r="U1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem Classification</t>
+          <t>DE Classification</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>Language Score</t>
+          <t>PL Score</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>Language Classification</t>
+          <t>PL Classification</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="AB1" s="8" t="inlineStr">
         <is>
-          <t>Domain MUST Valid</t>
+          <t>AD MUST Valid</t>
         </is>
       </c>
       <c r="AC1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem MUST Valid</t>
+          <t>DE MUST Valid</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>Language MUST Valid</t>
+          <t>PL MUST Valid</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="B2" s="15" t="inlineStr"/>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
@@ -1465,7 +1465,7 @@
       <c r="B3" s="9" t="inlineStr"/>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -1676,7 +1676,7 @@
       <c r="B4" s="9" t="inlineStr"/>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -1887,7 +1887,7 @@
       <c r="B5" s="9" t="inlineStr"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -2098,7 +2098,7 @@
       <c r="B6" s="9" t="inlineStr"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -2309,7 +2309,7 @@
       <c r="B7" s="9" t="inlineStr"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -2520,7 +2520,7 @@
       <c r="B8" s="9" t="inlineStr"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -2731,7 +2731,7 @@
       <c r="B9" s="9" t="inlineStr"/>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -2942,7 +2942,7 @@
       <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3153,7 +3153,7 @@
       <c r="B11" s="9" t="inlineStr"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -3364,7 +3364,7 @@
       <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -3575,7 +3575,7 @@
       <c r="B13" s="9" t="inlineStr"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -3997,7 +3997,7 @@
       <c r="B15" s="9" t="inlineStr"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -4208,7 +4208,7 @@
       <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -4419,7 +4419,7 @@
       <c r="B17" s="9" t="inlineStr"/>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -4630,7 +4630,7 @@
       <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -4841,7 +4841,7 @@
       <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -5052,7 +5052,7 @@
       <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -5263,7 +5263,7 @@
       <c r="B21" s="9" t="inlineStr"/>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -5586,77 +5586,77 @@
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>Domain MUST</t>
+          <t>AD MUST</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>Domain SHOULD</t>
+          <t>AD SHOULD</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>Domain COULD</t>
+          <t>AD COULD</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem MUST</t>
+          <t>DE MUST</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem SHOULD</t>
+          <t>DE SHOULD</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem COULD</t>
+          <t>DE COULD</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>Language MUST</t>
+          <t>PL MUST</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>Language SHOULD</t>
+          <t>PL SHOULD</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>Language COULD</t>
+          <t>PL COULD</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>Domain Score</t>
+          <t>AD Score</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>Domain Classification</t>
+          <t>AD Classification</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem Score</t>
+          <t>DE Score</t>
         </is>
       </c>
       <c r="U1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem Classification</t>
+          <t>DE Classification</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>Language Score</t>
+          <t>PL Score</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>Language Classification</t>
+          <t>PL Classification</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="AB1" s="8" t="inlineStr">
         <is>
-          <t>Domain MUST Valid</t>
+          <t>AD MUST Valid</t>
         </is>
       </c>
       <c r="AC1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem MUST Valid</t>
+          <t>DE MUST Valid</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>Language MUST Valid</t>
+          <t>PL MUST Valid</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
@@ -5774,7 +5774,7 @@
       <c r="B2" s="9" t="inlineStr"/>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>VienaSmart</t>
+          <t>ProjetoVS</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
